--- a/web_app/reports/latest_test_report.xlsx
+++ b/web_app/reports/latest_test_report.xlsx
@@ -592,7 +592,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated on: 2026-07-25 22:28:34  |  Environment: GitHub Actions / Local E2E Runner  |  Target Web App: GitHub Pages / Render</t>
+          <t>Generated on: 2026-07-28 10:13:18  |  Environment: GitHub Actions / Local E2E Runner  |  Target Web App: GitHub Pages / Render</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
         </is>
       </c>
       <c r="H69" s="16" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="I69" s="16" t="inlineStr">
         <is>
